--- a/database/seeders/excel/user.xlsx
+++ b/database/seeders/excel/user.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B91547-2367-4B9E-9C9C-1430AAD5E1A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2C16E6-C4D0-4005-BB14-A55721ACE13C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="214">
   <si>
     <t>nip_lama</t>
   </si>
@@ -663,109 +663,10 @@
     <t>198907202010122004</t>
   </si>
   <si>
-    <t>Ruang Aula</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Ruang Neraca</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Ruang Sosial</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Ruang Kepala - Kabag - Sekretaris</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Ruang SDM</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Ruang Keuangan</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Ruang Pajale</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Ruang IPDS</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Ruang PST</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Ruang Distribusi</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Ruang Madya</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Ruang Umum</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Ruang Garda</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Ruang Produksi</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Gudang</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Lelang</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Tidak Diketahui</t>
-  </si>
-  <si>
-    <t>99</t>
+    <t>is_jarkom</t>
+  </si>
+  <si>
+    <t>id_ruang</t>
   </si>
 </sst>
 </file>
@@ -1083,13 +984,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,8 +1007,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>340014249</v>
       </c>
@@ -1122,8 +1030,14 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>340014611</v>
       </c>
@@ -1139,8 +1053,14 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>340014682</v>
       </c>
@@ -1156,8 +1076,14 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>340016477</v>
       </c>
@@ -1173,8 +1099,14 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>340050052</v>
       </c>
@@ -1190,8 +1122,14 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>340016847</v>
       </c>
@@ -1207,8 +1145,14 @@
       <c r="E7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>340058230</v>
       </c>
@@ -1224,8 +1168,14 @@
       <c r="E8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>340018098</v>
       </c>
@@ -1241,8 +1191,14 @@
       <c r="E9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>340055841</v>
       </c>
@@ -1258,8 +1214,14 @@
       <c r="E10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>340054647</v>
       </c>
@@ -1275,8 +1237,14 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>340054663</v>
       </c>
@@ -1292,8 +1260,14 @@
       <c r="E12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>340057887</v>
       </c>
@@ -1309,8 +1283,14 @@
       <c r="E13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>340018099</v>
       </c>
@@ -1326,8 +1306,14 @@
       <c r="E14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>340018936</v>
       </c>
@@ -1343,8 +1329,14 @@
       <c r="E15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>340063668</v>
       </c>
@@ -1360,8 +1352,14 @@
       <c r="E16" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>340063944</v>
       </c>
@@ -1377,8 +1375,14 @@
       <c r="E17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>340013114</v>
       </c>
@@ -1394,8 +1398,14 @@
       <c r="E18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>340017517</v>
       </c>
@@ -1411,8 +1421,14 @@
       <c r="E19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>340054652</v>
       </c>
@@ -1428,8 +1444,14 @@
       <c r="E20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>340061101</v>
       </c>
@@ -1445,8 +1467,14 @@
       <c r="E21" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>340051219</v>
       </c>
@@ -1462,8 +1490,14 @@
       <c r="E22" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>340062133</v>
       </c>
@@ -1479,8 +1513,14 @@
       <c r="E23" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>340016846</v>
       </c>
@@ -1496,8 +1536,14 @@
       <c r="E24" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>340054662</v>
       </c>
@@ -1513,8 +1559,14 @@
       <c r="E25" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>340014688</v>
       </c>
@@ -1530,8 +1582,14 @@
       <c r="E26" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>340017519</v>
       </c>
@@ -1547,8 +1605,14 @@
       <c r="E27" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>340063917</v>
       </c>
@@ -1564,8 +1628,14 @@
       <c r="E28" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>340062122</v>
       </c>
@@ -1581,8 +1651,14 @@
       <c r="E29" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>340013729</v>
       </c>
@@ -1598,8 +1674,14 @@
       <c r="E30" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>340056007</v>
       </c>
@@ -1615,8 +1697,14 @@
       <c r="E31" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>340061235</v>
       </c>
@@ -1632,8 +1720,14 @@
       <c r="E32" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>340063997</v>
       </c>
@@ -1649,8 +1743,14 @@
       <c r="E33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>340065022</v>
       </c>
@@ -1666,8 +1766,14 @@
       <c r="E34" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>340065028</v>
       </c>
@@ -1683,8 +1789,14 @@
       <c r="E35" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>340065155</v>
       </c>
@@ -1700,8 +1812,14 @@
       <c r="E36" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>340065934</v>
       </c>
@@ -1717,8 +1835,14 @@
       <c r="E37" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>340065949</v>
       </c>
@@ -1734,8 +1858,14 @@
       <c r="E38" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>340016277</v>
       </c>
@@ -1751,8 +1881,14 @@
       <c r="E39" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>340016976</v>
       </c>
@@ -1768,8 +1904,14 @@
       <c r="E40" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>340015539</v>
       </c>
@@ -1785,8 +1927,14 @@
       <c r="E41" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>340020005</v>
       </c>
@@ -1802,8 +1950,14 @@
       <c r="E42" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>340016170</v>
       </c>
@@ -1819,8 +1973,14 @@
       <c r="E43" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>340015872</v>
       </c>
@@ -1836,8 +1996,14 @@
       <c r="E44" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>340057209</v>
       </c>
@@ -1853,8 +2019,14 @@
       <c r="E45" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>340054168</v>
       </c>
@@ -1870,8 +2042,14 @@
       <c r="E46" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>340057667</v>
       </c>
@@ -1887,8 +2065,14 @@
       <c r="E47" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>340016191</v>
       </c>
@@ -1904,8 +2088,14 @@
       <c r="E48" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>340016060</v>
       </c>
@@ -1921,8 +2111,14 @@
       <c r="E49" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>340053548</v>
       </c>
@@ -1938,8 +2134,14 @@
       <c r="E50" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>340017520</v>
       </c>
@@ -1955,8 +2157,14 @@
       <c r="E51" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>340054653</v>
       </c>
@@ -1972,8 +2180,14 @@
       <c r="E52" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>340058851</v>
       </c>
@@ -1989,8 +2203,14 @@
       <c r="E53" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>340018514</v>
       </c>
@@ -2006,8 +2226,14 @@
       <c r="E54" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>340060068</v>
       </c>
@@ -2023,8 +2249,14 @@
       <c r="E55" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>340015731</v>
       </c>
@@ -2040,8 +2272,14 @@
       <c r="E56" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>340054174</v>
       </c>
@@ -2057,8 +2295,14 @@
       <c r="E57" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>340016971</v>
       </c>
@@ -2074,8 +2318,14 @@
       <c r="E58" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>340019122</v>
       </c>
@@ -2091,8 +2341,14 @@
       <c r="E59" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>340059155</v>
       </c>
@@ -2108,8 +2364,14 @@
       <c r="E60" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>340056947</v>
       </c>
@@ -2125,8 +2387,14 @@
       <c r="E61" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>340055852</v>
       </c>
@@ -2142,8 +2410,14 @@
       <c r="E62" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>340013506</v>
       </c>
@@ -2159,8 +2433,14 @@
       <c r="E63" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>340062195</v>
       </c>
@@ -2176,8 +2456,14 @@
       <c r="E64" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340016973</v>
       </c>
@@ -2193,8 +2479,14 @@
       <c r="E65" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>340016187</v>
       </c>
@@ -2210,8 +2502,14 @@
       <c r="E66" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>340050143</v>
       </c>
@@ -2227,8 +2525,14 @@
       <c r="E67" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>340016574</v>
       </c>
@@ -2244,8 +2548,14 @@
       <c r="E68" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>340054175</v>
       </c>
@@ -2261,8 +2571,14 @@
       <c r="E69" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>340060289</v>
       </c>
@@ -2278,8 +2594,14 @@
       <c r="E70" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>340058939</v>
       </c>
@@ -2295,8 +2617,14 @@
       <c r="E71" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>340056458</v>
       </c>
@@ -2312,8 +2640,14 @@
       <c r="E72" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>340059165</v>
       </c>
@@ -2329,8 +2663,14 @@
       <c r="E73" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>340013013</v>
       </c>
@@ -2346,8 +2686,14 @@
       <c r="E74" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>340016975</v>
       </c>
@@ -2363,8 +2709,14 @@
       <c r="E75" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>340055712</v>
       </c>
@@ -2380,8 +2732,14 @@
       <c r="E76" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>340053273</v>
       </c>
@@ -2397,8 +2755,14 @@
       <c r="E77" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>340056760</v>
       </c>
@@ -2414,8 +2778,14 @@
       <c r="E78" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>340060080</v>
       </c>
@@ -2431,8 +2801,14 @@
       <c r="E79" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>340058485</v>
       </c>
@@ -2448,8 +2824,14 @@
       <c r="E80" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>340059630</v>
       </c>
@@ -2465,8 +2847,14 @@
       <c r="E81" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>340057694</v>
       </c>
@@ -2482,8 +2870,14 @@
       <c r="E82" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>340066553</v>
       </c>
@@ -2499,8 +2893,14 @@
       <c r="E83" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>340061727</v>
       </c>
@@ -2516,8 +2916,14 @@
       <c r="E84" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>340054170</v>
       </c>
@@ -2533,294 +2939,11 @@
       <c r="E85" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86">
+      <c r="F85">
         <v>1</v>
       </c>
-      <c r="B86" t="s">
-        <v>212</v>
-      </c>
-      <c r="C86" t="s">
-        <v>213</v>
-      </c>
-      <c r="D86">
-        <v>3</v>
-      </c>
-      <c r="E86" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>2</v>
-      </c>
-      <c r="B87" t="s">
-        <v>215</v>
-      </c>
-      <c r="C87" t="s">
-        <v>216</v>
-      </c>
-      <c r="D87">
+      <c r="G85">
         <v>8</v>
-      </c>
-      <c r="E87" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>3</v>
-      </c>
-      <c r="B88" t="s">
-        <v>217</v>
-      </c>
-      <c r="C88" t="s">
-        <v>218</v>
-      </c>
-      <c r="D88">
-        <v>5</v>
-      </c>
-      <c r="E88" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>4</v>
-      </c>
-      <c r="B89" t="s">
-        <v>219</v>
-      </c>
-      <c r="C89" t="s">
-        <v>220</v>
-      </c>
-      <c r="D89">
-        <v>3</v>
-      </c>
-      <c r="E89" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>5</v>
-      </c>
-      <c r="B90" t="s">
-        <v>221</v>
-      </c>
-      <c r="C90" t="s">
-        <v>222</v>
-      </c>
-      <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>6</v>
-      </c>
-      <c r="B91" t="s">
-        <v>223</v>
-      </c>
-      <c r="C91" t="s">
-        <v>224</v>
-      </c>
-      <c r="D91">
-        <v>3</v>
-      </c>
-      <c r="E91" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>7</v>
-      </c>
-      <c r="B92" t="s">
-        <v>225</v>
-      </c>
-      <c r="C92" t="s">
-        <v>226</v>
-      </c>
-      <c r="D92">
-        <v>3</v>
-      </c>
-      <c r="E92" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>8</v>
-      </c>
-      <c r="B93" t="s">
-        <v>227</v>
-      </c>
-      <c r="C93" t="s">
-        <v>228</v>
-      </c>
-      <c r="D93">
-        <v>9</v>
-      </c>
-      <c r="E93" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>9</v>
-      </c>
-      <c r="B94" t="s">
-        <v>229</v>
-      </c>
-      <c r="C94" t="s">
-        <v>230</v>
-      </c>
-      <c r="D94">
-        <v>9</v>
-      </c>
-      <c r="E94" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>10</v>
-      </c>
-      <c r="B95" t="s">
-        <v>231</v>
-      </c>
-      <c r="C95" t="s">
-        <v>232</v>
-      </c>
-      <c r="D95">
-        <v>7</v>
-      </c>
-      <c r="E95" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>11</v>
-      </c>
-      <c r="B96" t="s">
-        <v>233</v>
-      </c>
-      <c r="C96" t="s">
-        <v>234</v>
-      </c>
-      <c r="D96">
-        <v>3</v>
-      </c>
-      <c r="E96" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>12</v>
-      </c>
-      <c r="B97" t="s">
-        <v>235</v>
-      </c>
-      <c r="C97" t="s">
-        <v>236</v>
-      </c>
-      <c r="D97">
-        <v>3</v>
-      </c>
-      <c r="E97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>13</v>
-      </c>
-      <c r="B98" t="s">
-        <v>237</v>
-      </c>
-      <c r="C98" t="s">
-        <v>238</v>
-      </c>
-      <c r="D98">
-        <v>3</v>
-      </c>
-      <c r="E98" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>14</v>
-      </c>
-      <c r="B99" t="s">
-        <v>239</v>
-      </c>
-      <c r="C99" t="s">
-        <v>240</v>
-      </c>
-      <c r="D99">
-        <v>6</v>
-      </c>
-      <c r="E99" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>241</v>
-      </c>
-      <c r="C100" t="s">
-        <v>242</v>
-      </c>
-      <c r="D100">
-        <v>3</v>
-      </c>
-      <c r="E100" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>16</v>
-      </c>
-      <c r="B101" t="s">
-        <v>243</v>
-      </c>
-      <c r="C101" t="s">
-        <v>244</v>
-      </c>
-      <c r="D101">
-        <v>3</v>
-      </c>
-      <c r="E101" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>99</v>
-      </c>
-      <c r="B102" t="s">
-        <v>245</v>
-      </c>
-      <c r="C102" t="s">
-        <v>246</v>
-      </c>
-      <c r="D102">
-        <v>99</v>
-      </c>
-      <c r="E102" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
